--- a/data/templates/Digital_Asset_Template.xlsx
+++ b/data/templates/Digital_Asset_Template.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
   <si>
     <t>ID</t>
   </si>
@@ -129,33 +129,15 @@
     <t>Issue - 02</t>
   </si>
   <si>
-    <t>manual/pdf-download-accessibility</t>
-  </si>
-  <si>
-    <t>Ensure downloaded PDF documents are accessible and usable with assistive technologies</t>
-  </si>
-  <si>
-    <t>Issue - 02 - manual/pdf-download-accessibility - 8th Edition Chapter 11 Case 1 - Ensure downloaded PDF documents are accessible and usable with assistive technologies</t>
-  </si>
-  <si>
     <t>manual/powerpoint-download-accessibility</t>
   </si>
   <si>
     <t>Ensure downloaded Power Point documents are accessible and usable with assistive technologies</t>
   </si>
   <si>
-    <t>Issue - 03</t>
-  </si>
-  <si>
-    <t>Issue - 03 - manual/powerpoint-download-accessibility - Image Bank: Chapter 31 - Ensure downloaded Power Point documents are accessible and usable with assistive technologies</t>
-  </si>
-  <si>
     <t xml:space="preserve">All Word documents </t>
   </si>
   <si>
-    <t xml:space="preserve">All PDF documents </t>
-  </si>
-  <si>
     <t xml:space="preserve">All Power Point documents </t>
   </si>
   <si>
@@ -163,9 +145,6 @@
   </si>
   <si>
     <t>PowerPoint (.ppt/.pptx)</t>
-  </si>
-  <si>
-    <t>PDF documents (.pdf)</t>
   </si>
   <si>
     <t>HOW TO FIX - 
@@ -182,20 +161,6 @@
 Microsoft Word Accessibility Checker
 Screen reader testing (NVDA, JAWS, or Narrator)
 Keyboard-only navigation testing</t>
-  </si>
-  <si>
-    <t>HOW TO FIX - 
-Validate the downloaded PDF and ensure:
-Proper PDF tagging structure
-Logical reading order
-Accessible document headings and semantics
-Alternative text for meaningful images
-Document title and language metadata
-Screen reader compatibility
-Test using:
-PAC (PDF Accessibility Checker)
-Adobe Acrobat Accessibility Checker
-Screen reader testing</t>
   </si>
   <si>
     <t>HOW TO FIX - 
@@ -252,35 +217,6 @@
   </si>
   <si>
     <t>Issue Type:
-manual/pdf-download-accessibility
-Root Cause:
-Publisher / Content Author
-Issue:
-Ensure downloaded PDF documents are accessible and usable with assistive technologies
-Element:
-PDF documents (.pdf)
-Resolution:
-- HOW TO FIX -
-Validate the downloaded PDF and ensure:
-Proper PDF tagging structure
-Logical reading order
-Accessible document headings and semantics
-Alternative text for meaningful images
-Document title and language metadata
-Screen reader compatibility
-Test using:
-PAC (PDF Accessibility Checker)
-Adobe Acrobat Accessibility Checker
-Screen reader testing
-Fix Owner:
-Publisher / Content Author
-WCAG Ref:
-Ref: 1.3.1
-WCAG:
-1.3.1 Info and Relationships</t>
-  </si>
-  <si>
-    <t>Issue Type:
 manual/powerpoint-download-accessibility
 Root Cause:
 Publisher / Content Author
@@ -312,6 +248,9 @@
   </si>
   <si>
     <t>Story</t>
+  </si>
+  <si>
+    <t>Issue - 02 - manual/powerpoint-download-accessibility - Image Bank: Chapter 31 - Ensure downloaded Power Point documents are accessible and usable with assistive technologies</t>
   </si>
 </sst>
 </file>
@@ -624,7 +563,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -632,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="27.90625" customWidth="1"/>
@@ -727,7 +666,7 @@
         <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
         <v>27</v>
@@ -736,10 +675,10 @@
         <v>28</v>
       </c>
       <c r="H2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="K2" t="s">
         <v>26</v>
@@ -754,7 +693,7 @@
         <v>30</v>
       </c>
       <c r="O2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="P2" t="s">
         <v>31</v>
@@ -763,13 +702,13 @@
         <v>32</v>
       </c>
       <c r="R2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="S2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="U2" t="s">
         <v>24</v>
@@ -795,7 +734,7 @@
         <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
         <v>27</v>
@@ -804,10 +743,10 @@
         <v>37</v>
       </c>
       <c r="H3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K3" t="s">
         <v>26</v>
@@ -822,7 +761,7 @@
         <v>30</v>
       </c>
       <c r="O3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="P3" t="s">
         <v>31</v>
@@ -831,13 +770,13 @@
         <v>32</v>
       </c>
       <c r="R3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="S3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="U3" t="s">
         <v>24</v>
@@ -846,74 +785,6 @@
         <v>33</v>
       </c>
       <c r="W3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" t="s">
-        <v>30</v>
-      </c>
-      <c r="O4" t="s">
-        <v>53</v>
-      </c>
-      <c r="P4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>32</v>
-      </c>
-      <c r="R4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S4" t="s">
-        <v>42</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="U4" t="s">
-        <v>24</v>
-      </c>
-      <c r="V4" t="s">
-        <v>33</v>
-      </c>
-      <c r="W4" t="s">
         <v>34</v>
       </c>
     </row>
